--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
@@ -565,13 +565,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>110.8999</v>
+        <v>106.296</v>
       </c>
       <c r="E2" t="n">
-        <v>94.8711</v>
+        <v>87.69710000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>16.029</v>
+        <v>18.5991</v>
       </c>
       <c r="G2" t="n">
         <v>48.474</v>
@@ -610,13 +610,13 @@
         <v>48.9612</v>
       </c>
       <c r="S2" t="n">
-        <v>25.6772</v>
+        <v>21.0731</v>
       </c>
       <c r="T2" t="n">
-        <v>23.4678</v>
+        <v>16.2938</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2091</v>
+        <v>4.7793</v>
       </c>
       <c r="V2" t="n">
         <v>20.2965</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>65.15599999999999</v>
+        <v>67.5926</v>
       </c>
       <c r="E3" t="n">
-        <v>44.7761</v>
+        <v>50.5814</v>
       </c>
       <c r="F3" t="n">
-        <v>20.3796</v>
+        <v>17.0117</v>
       </c>
       <c r="G3" t="n">
-        <v>3.975499999999998</v>
+        <v>20.2733</v>
       </c>
       <c r="H3" t="n">
-        <v>6.550800000000001</v>
+        <v>13.2819</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5756</v>
+        <v>6.9909</v>
       </c>
       <c r="J3" t="n">
-        <v>21.2342</v>
+        <v>35.4812</v>
       </c>
       <c r="K3" t="n">
-        <v>20.3719</v>
+        <v>24.0966</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8618999999999997</v>
+        <v>11.3849</v>
       </c>
       <c r="M3" t="n">
-        <v>-17.2587</v>
+        <v>-15.2084</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.8217</v>
+        <v>-10.8146</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.437000000000001</v>
+        <v>-4.393600000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.3341</v>
+        <v>24.3814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48.7626</v>
+        <v>-23.9847</v>
       </c>
       <c r="R3" t="n">
-        <v>41.4287</v>
+        <v>48.3664</v>
       </c>
       <c r="S3" t="n">
-        <v>52.2724</v>
+        <v>13.4253</v>
       </c>
       <c r="T3" t="n">
-        <v>24.5288</v>
+        <v>10.7329</v>
       </c>
       <c r="U3" t="n">
-        <v>27.7435</v>
+        <v>2.6922</v>
       </c>
       <c r="V3" t="n">
-        <v>16.2427</v>
+        <v>9.5129</v>
       </c>
       <c r="W3" t="n">
-        <v>47.7765</v>
+        <v>28.3523</v>
       </c>
       <c r="X3" t="n">
-        <v>-31.5339</v>
+        <v>-18.8391</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>63.9215</v>
+        <v>61.9192</v>
       </c>
       <c r="E4" t="n">
-        <v>49.9904</v>
+        <v>40.2167</v>
       </c>
       <c r="F4" t="n">
-        <v>13.9314</v>
+        <v>21.7028</v>
       </c>
       <c r="G4" t="n">
-        <v>20.2733</v>
+        <v>1.964600000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>13.2819</v>
+        <v>13.5331</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9909</v>
+        <v>-11.5683</v>
       </c>
       <c r="J4" t="n">
-        <v>35.4812</v>
+        <v>28.0882</v>
       </c>
       <c r="K4" t="n">
-        <v>24.0966</v>
+        <v>31.7493</v>
       </c>
       <c r="L4" t="n">
-        <v>11.3849</v>
+        <v>-3.661</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.2084</v>
+        <v>-26.1238</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.8146</v>
+        <v>-18.2165</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.393600000000001</v>
+        <v>-7.9072</v>
       </c>
       <c r="P4" t="n">
-        <v>24.3814</v>
+        <v>20.0204</v>
       </c>
       <c r="Q4" t="n">
-        <v>-23.9847</v>
+        <v>-36.8691</v>
       </c>
       <c r="R4" t="n">
-        <v>48.3664</v>
+        <v>56.89</v>
       </c>
       <c r="S4" t="n">
-        <v>9.754100000000001</v>
+        <v>18.5377</v>
       </c>
       <c r="T4" t="n">
-        <v>10.1421</v>
+        <v>13.3928</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3882000000000001</v>
+        <v>5.145</v>
       </c>
       <c r="V4" t="n">
-        <v>9.5129</v>
+        <v>21.396</v>
       </c>
       <c r="W4" t="n">
-        <v>28.3523</v>
+        <v>35.6047</v>
       </c>
       <c r="X4" t="n">
-        <v>-18.8391</v>
+        <v>-14.2087</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>59.8987</v>
+        <v>50.5269</v>
       </c>
       <c r="E5" t="n">
-        <v>42.3106</v>
+        <v>37.4733</v>
       </c>
       <c r="F5" t="n">
-        <v>17.588</v>
+        <v>13.0536</v>
       </c>
       <c r="G5" t="n">
         <v>24.0052</v>
@@ -844,13 +844,13 @@
         <v>26.76</v>
       </c>
       <c r="S5" t="n">
-        <v>25.6418</v>
+        <v>16.27</v>
       </c>
       <c r="T5" t="n">
-        <v>13.6246</v>
+        <v>8.7872</v>
       </c>
       <c r="U5" t="n">
-        <v>12.0171</v>
+        <v>7.4828</v>
       </c>
       <c r="V5" t="n">
         <v>-4.8134</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>54.3702</v>
+        <v>47.0613</v>
       </c>
       <c r="E6" t="n">
-        <v>35.9685</v>
+        <v>47.0613</v>
       </c>
       <c r="F6" t="n">
-        <v>18.4019</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.964600000000002</v>
+        <v>47.0613</v>
       </c>
       <c r="H6" t="n">
-        <v>13.5331</v>
+        <v>12.1067</v>
       </c>
       <c r="I6" t="n">
-        <v>-11.5683</v>
+        <v>34.9546</v>
       </c>
       <c r="J6" t="n">
-        <v>28.0882</v>
+        <v>47.0613</v>
       </c>
       <c r="K6" t="n">
-        <v>31.7493</v>
+        <v>12.1067</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.661</v>
+        <v>34.9546</v>
       </c>
       <c r="M6" t="n">
-        <v>-26.1238</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-18.2165</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.9072</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>20.0204</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-36.8691</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>56.89</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>10.9892</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>9.1448</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8443</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>21.396</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>35.6047</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.2087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>53.7047</v>
+        <v>44.4025</v>
       </c>
       <c r="E7" t="n">
-        <v>36.6498</v>
+        <v>36.4089</v>
       </c>
       <c r="F7" t="n">
-        <v>17.0552</v>
+        <v>7.993600000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>17.9383</v>
+        <v>3.975499999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>17.784</v>
+        <v>6.550800000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1542999999999998</v>
+        <v>-2.5756</v>
       </c>
       <c r="J7" t="n">
-        <v>38.9302</v>
+        <v>21.2342</v>
       </c>
       <c r="K7" t="n">
-        <v>31.6943</v>
+        <v>20.3719</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2361</v>
+        <v>0.8618999999999997</v>
       </c>
       <c r="M7" t="n">
-        <v>-20.9917</v>
+        <v>-17.2587</v>
       </c>
       <c r="N7" t="n">
-        <v>-13.9101</v>
+        <v>-13.8217</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.0815</v>
+        <v>-3.437000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>11.4968</v>
+        <v>-7.3341</v>
       </c>
       <c r="Q7" t="n">
-        <v>-39.6442</v>
+        <v>-48.7626</v>
       </c>
       <c r="R7" t="n">
-        <v>51.1413</v>
+        <v>41.4287</v>
       </c>
       <c r="S7" t="n">
-        <v>36.4294</v>
+        <v>31.5185</v>
       </c>
       <c r="T7" t="n">
-        <v>29.4778</v>
+        <v>16.1616</v>
       </c>
       <c r="U7" t="n">
-        <v>6.9515</v>
+        <v>15.3571</v>
       </c>
       <c r="V7" t="n">
-        <v>-12.1598</v>
+        <v>16.2427</v>
       </c>
       <c r="W7" t="n">
-        <v>7.8865</v>
+        <v>47.7765</v>
       </c>
       <c r="X7" t="n">
-        <v>-20.0462</v>
+        <v>-31.5339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>47.0613</v>
+        <v>37.5148</v>
       </c>
       <c r="E8" t="n">
-        <v>47.0613</v>
+        <v>22.1014</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>15.4132</v>
       </c>
       <c r="G8" t="n">
-        <v>47.0613</v>
+        <v>17.9383</v>
       </c>
       <c r="H8" t="n">
-        <v>12.1067</v>
+        <v>17.784</v>
       </c>
       <c r="I8" t="n">
-        <v>34.9546</v>
+        <v>0.1542999999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>47.0613</v>
+        <v>38.9302</v>
       </c>
       <c r="K8" t="n">
-        <v>12.1067</v>
+        <v>31.6943</v>
       </c>
       <c r="L8" t="n">
-        <v>34.9546</v>
+        <v>7.2361</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-20.9917</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-13.9101</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-7.0815</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11.4968</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-39.6442</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>51.1413</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>20.2392</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>14.9297</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.3098</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-12.1598</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>7.8865</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-20.0462</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>19.9203</v>
+        <v>31.477</v>
       </c>
       <c r="E9" t="n">
-        <v>19.9203</v>
+        <v>23.0079</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>8.4694</v>
       </c>
       <c r="G9" t="n">
-        <v>19.9203</v>
+        <v>29.8141</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2643</v>
+        <v>20.3658</v>
       </c>
       <c r="I9" t="n">
-        <v>12.6561</v>
+        <v>9.4481</v>
       </c>
       <c r="J9" t="n">
-        <v>19.9203</v>
+        <v>52.9839</v>
       </c>
       <c r="K9" t="n">
-        <v>7.2643</v>
+        <v>33.5004</v>
       </c>
       <c r="L9" t="n">
-        <v>12.6561</v>
+        <v>19.4838</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-23.1702</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-13.1346</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-10.0356</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-49.9519</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>47.5737</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>10.4847</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>6.3206</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.1642</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-6.4431</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>13.6554</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-20.0987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>17.0943</v>
+        <v>19.9203</v>
       </c>
       <c r="E10" t="n">
-        <v>13.3903</v>
+        <v>19.9203</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7044</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>29.8141</v>
+        <v>19.9203</v>
       </c>
       <c r="H10" t="n">
-        <v>20.3658</v>
+        <v>7.2643</v>
       </c>
       <c r="I10" t="n">
-        <v>9.4481</v>
+        <v>12.6561</v>
       </c>
       <c r="J10" t="n">
-        <v>52.9839</v>
+        <v>19.9203</v>
       </c>
       <c r="K10" t="n">
-        <v>33.5004</v>
+        <v>7.2643</v>
       </c>
       <c r="L10" t="n">
-        <v>19.4838</v>
+        <v>12.6561</v>
       </c>
       <c r="M10" t="n">
-        <v>-23.1702</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-13.1346</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.0356</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-49.9519</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>47.5737</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.8979</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.297</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.601</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.4431</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>13.6554</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-20.0987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>16.6066</v>
+        <v>18.0809</v>
       </c>
       <c r="E11" t="n">
-        <v>16.6066</v>
+        <v>17.516</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.5649999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>16.6066</v>
+        <v>5.117599999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>7.567</v>
+        <v>-0.4745999999999995</v>
       </c>
       <c r="I11" t="n">
-        <v>9.0404</v>
+        <v>5.592000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>16.6066</v>
+        <v>13.7753</v>
       </c>
       <c r="K11" t="n">
-        <v>7.567</v>
+        <v>5.3832</v>
       </c>
       <c r="L11" t="n">
-        <v>9.0404</v>
+        <v>8.392199999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-8.657999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-5.8578</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-2.7999</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10.5057</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.9555</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>15.4614</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>6.861800000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.5421</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.3201</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-4.404</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.1546</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-8.5585</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6897</v>
+        <v>18.0388</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.579599999999999</v>
+        <v>-6.1717</v>
       </c>
       <c r="F12" t="n">
-        <v>20.2693</v>
+        <v>24.2107</v>
       </c>
       <c r="G12" t="n">
         <v>-11.4887</v>
@@ -1390,13 +1390,13 @@
         <v>38.8516</v>
       </c>
       <c r="S12" t="n">
-        <v>7.8377</v>
+        <v>14.1866</v>
       </c>
       <c r="T12" t="n">
-        <v>8.3649</v>
+        <v>10.7732</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5276999999999999</v>
+        <v>3.414</v>
       </c>
       <c r="V12" t="n">
         <v>7.0152</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>10.5648</v>
+        <v>16.6066</v>
       </c>
       <c r="E13" t="n">
-        <v>11.0296</v>
+        <v>16.6066</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4647999999999992</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5.117599999999999</v>
+        <v>16.6066</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4745999999999995</v>
+        <v>7.567</v>
       </c>
       <c r="I13" t="n">
-        <v>5.592000000000001</v>
+        <v>9.0404</v>
       </c>
       <c r="J13" t="n">
-        <v>13.7753</v>
+        <v>16.6066</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3832</v>
+        <v>7.567</v>
       </c>
       <c r="L13" t="n">
-        <v>8.392199999999999</v>
+        <v>9.0404</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.657999999999999</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.8578</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.7999</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10.5057</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.9555</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>15.4614</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6546</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9447</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2902</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.404</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1546</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.5585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3222</v>
+        <v>8.4415</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2846</v>
+        <v>-2.2507</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0377</v>
+        <v>10.6923</v>
       </c>
       <c r="G14" t="n">
-        <v>4.158</v>
+        <v>-25.6641</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5024</v>
+        <v>-9.7037</v>
       </c>
       <c r="I14" t="n">
-        <v>4.660299999999999</v>
+        <v>-15.9606</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3038</v>
+        <v>-1.0874</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.8428</v>
+        <v>9.9419</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1466</v>
+        <v>-11.0293</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8541</v>
+        <v>-24.5769</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3405</v>
+        <v>-19.6456</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4863000000000001</v>
+        <v>-4.931</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1893</v>
+        <v>1.585899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.1626</v>
+        <v>-44.2032</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9734</v>
+        <v>45.7894</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5013</v>
+        <v>9.727</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8769</v>
+        <v>6.3246</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3757</v>
+        <v>3.4026</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.1477</v>
+        <v>22.7932</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2666</v>
+        <v>36.7162</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4143</v>
+        <v>-13.9231</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LOPEZ PERAGON</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.3749</v>
+        <v>3.129</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.325900000000001</v>
+        <v>1.1475</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.049</v>
+        <v>1.9815</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.162000000000001</v>
+        <v>4.158</v>
       </c>
       <c r="H16" t="n">
-        <v>0.285</v>
+        <v>-0.5024</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.447100000000001</v>
+        <v>4.660299999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.3608</v>
+        <v>2.3038</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3775000000000002</v>
+        <v>-2.8428</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.738300000000001</v>
+        <v>5.1466</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8013</v>
+        <v>1.8541</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.09259999999999996</v>
+        <v>2.3405</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7088</v>
+        <v>-0.4863000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5768</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.127000000000001</v>
+        <v>-4.1626</v>
       </c>
       <c r="R16" t="n">
-        <v>5.5502</v>
+        <v>2.9734</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3693</v>
+        <v>2.308</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4811</v>
+        <v>2.7397</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.8506</v>
+        <v>-0.4318</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2665999999999998</v>
+        <v>-2.1477</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6808</v>
+        <v>0.2666</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.9474</v>
+        <v>-2.4143</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.1308</v>
+        <v>-3.188900000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.3483</v>
+        <v>-9.7103</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2174</v>
+        <v>6.5211</v>
       </c>
       <c r="G17" t="n">
-        <v>-25.6641</v>
+        <v>-3.7068</v>
       </c>
       <c r="H17" t="n">
-        <v>-9.7037</v>
+        <v>-1.6752</v>
       </c>
       <c r="I17" t="n">
-        <v>-15.9606</v>
+        <v>-2.032</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0874</v>
+        <v>15.2242</v>
       </c>
       <c r="K17" t="n">
-        <v>9.9419</v>
+        <v>8.8607</v>
       </c>
       <c r="L17" t="n">
-        <v>-11.0293</v>
+        <v>6.3636</v>
       </c>
       <c r="M17" t="n">
-        <v>-24.5769</v>
+        <v>-18.9309</v>
       </c>
       <c r="N17" t="n">
-        <v>-19.6456</v>
+        <v>-10.536</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.931</v>
+        <v>-8.3956</v>
       </c>
       <c r="P17" t="n">
-        <v>1.585899999999999</v>
+        <v>-14.0737</v>
       </c>
       <c r="Q17" t="n">
-        <v>-44.2032</v>
+        <v>-47.9697</v>
       </c>
       <c r="R17" t="n">
-        <v>45.7894</v>
+        <v>33.8962</v>
       </c>
       <c r="S17" t="n">
-        <v>-10.846</v>
+        <v>5.2546</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.7733</v>
+        <v>3.3448</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.0724</v>
+        <v>1.9102</v>
       </c>
       <c r="V17" t="n">
-        <v>22.7932</v>
+        <v>9.3368</v>
       </c>
       <c r="W17" t="n">
-        <v>36.7162</v>
+        <v>19.691</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.9231</v>
+        <v>-10.3542</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>M. LOPEZ PERAGON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-13.9163</v>
+        <v>-9.1982</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.0477</v>
+        <v>-9.099299999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8686</v>
+        <v>-0.09910000000000013</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.3594</v>
+        <v>-6.162000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.5821</v>
+        <v>0.285</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.7772</v>
+        <v>-6.447100000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.2848</v>
+        <v>-4.3608</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7607</v>
+        <v>0.3775000000000002</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5241</v>
+        <v>-4.738300000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-7.0743</v>
+        <v>-1.8013</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.8214</v>
+        <v>-0.09259999999999996</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.2532</v>
+        <v>-1.7088</v>
       </c>
       <c r="P18" t="n">
-        <v>3.9644</v>
+        <v>-2.5768</v>
       </c>
       <c r="Q18" t="n">
-        <v>-8.126999999999999</v>
+        <v>-8.127000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>12.0915</v>
+        <v>5.5502</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4952000000000001</v>
+        <v>-0.1925999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3749</v>
+        <v>0.7079000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1202999999999999</v>
+        <v>-0.9006000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-8.017200000000001</v>
+        <v>-0.2665999999999998</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.0109</v>
+        <v>2.6808</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.0063</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>-16.3938</v>
+        <v>-12.9895</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.5296</v>
+        <v>-10.5593</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1358</v>
+        <v>-2.4303</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7068</v>
+        <v>-10.3594</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6752</v>
+        <v>-5.5821</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.032</v>
+        <v>-4.7772</v>
       </c>
       <c r="J19" t="n">
-        <v>15.2242</v>
+        <v>-3.2848</v>
       </c>
       <c r="K19" t="n">
-        <v>8.8607</v>
+        <v>-1.7607</v>
       </c>
       <c r="L19" t="n">
-        <v>6.3636</v>
+        <v>-1.5241</v>
       </c>
       <c r="M19" t="n">
-        <v>-18.9309</v>
+        <v>-7.0743</v>
       </c>
       <c r="N19" t="n">
-        <v>-10.536</v>
+        <v>-3.8214</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.3956</v>
+        <v>-3.2532</v>
       </c>
       <c r="P19" t="n">
-        <v>-14.0737</v>
+        <v>3.9644</v>
       </c>
       <c r="Q19" t="n">
-        <v>-47.9697</v>
+        <v>-8.126999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>33.8962</v>
+        <v>12.0915</v>
       </c>
       <c r="S19" t="n">
-        <v>-7.9503</v>
+        <v>1.4226</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.4748</v>
+        <v>1.8637</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.4754</v>
+        <v>-0.4412</v>
       </c>
       <c r="V19" t="n">
-        <v>9.3368</v>
+        <v>-8.017200000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>19.691</v>
+        <v>-1.0109</v>
       </c>
       <c r="X19" t="n">
-        <v>-10.3542</v>
+        <v>-7.0063</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>485.7158000000001</v>
+        <v>508.9521999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>354.3494999999999</v>
+        <v>365.2685</v>
       </c>
       <c r="F20" t="n">
-        <v>131.3673</v>
+        <v>143.6846</v>
       </c>
       <c r="G20" t="n">
         <v>185.2492</v>
@@ -1984,7 +1984,7 @@
         <v>118.201</v>
       </c>
       <c r="I20" t="n">
-        <v>67.04760000000002</v>
+        <v>67.0476</v>
       </c>
       <c r="J20" t="n">
         <v>396.2405</v>
@@ -2005,7 +2005,7 @@
         <v>-72.00359999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>84.2449</v>
+        <v>84.24489999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>-391.487</v>
@@ -2014,13 +2014,13 @@
         <v>475.735</v>
       </c>
       <c r="S20" t="n">
-        <v>147.8802</v>
+        <v>171.1165</v>
       </c>
       <c r="T20" t="n">
-        <v>105.9939</v>
+        <v>116.9146</v>
       </c>
       <c r="U20" t="n">
-        <v>41.885</v>
+        <v>54.2037</v>
       </c>
       <c r="V20" t="n">
         <v>68.3415</v>
